--- a/data/trans_orig/P29-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P29-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2007</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>128722</t>
+          <t>127758</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>171438</t>
+          <t>170144</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>322763</t>
+          <t>321529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>374147</t>
+          <t>375105</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>459819</t>
+          <t>466552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>532103</t>
+          <t>531913</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88810</t>
+          <t>90213</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>127706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138673</t>
+          <t>138294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>182327</t>
+          <t>181840</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>238118</t>
+          <t>239540</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>296316</t>
+          <t>297360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,51%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>414054</t>
+          <t>413805</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>463237</t>
+          <t>465746</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>161130</t>
+          <t>157740</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203351</t>
+          <t>202911</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>582603</t>
+          <t>584250</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>655879</t>
+          <t>654985</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197219</t>
+          <t>198981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>253392</t>
+          <t>253099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>478738</t>
+          <t>481188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>543110</t>
+          <t>543259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>694677</t>
+          <t>691133</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>779755</t>
+          <t>779423</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134048</t>
+          <t>134277</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>182784</t>
+          <t>179614</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>153434</t>
+          <t>154201</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>201881</t>
+          <t>200587</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>298749</t>
+          <t>300881</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>364867</t>
+          <t>368806</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>547390</t>
+          <t>549197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>613116</t>
+          <t>611277</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>252940</t>
+          <t>251159</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>311021</t>
+          <t>312930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>816440</t>
+          <t>812454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>900955</t>
+          <t>901910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,73%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>190950</t>
+          <t>189354</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>240842</t>
+          <t>242659</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>355829</t>
+          <t>354104</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>407043</t>
+          <t>406059</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>556129</t>
+          <t>561465</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>631522</t>
+          <t>637741</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110488</t>
+          <t>112907</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>154984</t>
+          <t>153996</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151983</t>
+          <t>151448</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>198004</t>
+          <t>194717</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>277311</t>
+          <t>278172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>337649</t>
+          <t>339414</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>303990</t>
+          <t>301392</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358003</t>
+          <t>356260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111504</t>
+          <t>109860</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151346</t>
+          <t>152400</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>425864</t>
+          <t>424656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>498279</t>
+          <t>496661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,46%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>241497</t>
+          <t>238561</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>294578</t>
+          <t>294141</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>514341</t>
+          <t>513083</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>577686</t>
+          <t>577850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>769570</t>
+          <t>766347</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>856785</t>
+          <t>855910</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126945</t>
+          <t>127460</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169469</t>
+          <t>171302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>164215</t>
+          <t>163059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>215586</t>
+          <t>211396</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300961</t>
+          <t>304605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367392</t>
+          <t>368025</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>496844</t>
+          <t>499278</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>555314</t>
+          <t>560766</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>277696</t>
+          <t>279616</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>335377</t>
+          <t>338183</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>791847</t>
+          <t>786521</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>879683</t>
+          <t>878073</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>804658</t>
+          <t>802564</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>906429</t>
+          <t>900023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1728429</t>
+          <t>1719761</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1839822</t>
+          <t>1847016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2556065</t>
+          <t>2563608</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2716679</t>
+          <t>2717815</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>500418</t>
+          <t>503282</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>586846</t>
+          <t>587875</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>653414</t>
+          <t>649158</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>748064</t>
+          <t>746706</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1174469</t>
+          <t>1177769</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1302182</t>
+          <t>1307266</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1821344</t>
+          <t>1829096</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1937089</t>
+          <t>1937077</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>844598</t>
+          <t>842806</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>949631</t>
+          <t>949667</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2705088</t>
+          <t>2701121</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2865563</t>
+          <t>2862436</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2012</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>159227</t>
+          <t>157287</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205655</t>
+          <t>206124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>389678</t>
+          <t>393336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>444634</t>
+          <t>446324</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>558698</t>
+          <t>561533</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>637228</t>
+          <t>639351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78451</t>
+          <t>77646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114600</t>
+          <t>114019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83729</t>
+          <t>83125</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122016</t>
+          <t>121611</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171109</t>
+          <t>173566</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224482</t>
+          <t>224707</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>401048</t>
+          <t>402516</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>454475</t>
+          <t>456654</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>153497</t>
+          <t>152766</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>200705</t>
+          <t>200626</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>565994</t>
+          <t>565668</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>645979</t>
+          <t>642399</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>258547</t>
+          <t>255846</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>318653</t>
+          <t>313260</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>569618</t>
+          <t>570513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>630026</t>
+          <t>635198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>840524</t>
+          <t>843274</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>929872</t>
+          <t>934712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,59%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>114654</t>
+          <t>115334</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>159873</t>
+          <t>159986</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>111599</t>
+          <t>110225</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>154437</t>
+          <t>155148</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>240839</t>
+          <t>236129</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>300132</t>
+          <t>302655</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>560568</t>
+          <t>563704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>625400</t>
+          <t>630019</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>267398</t>
+          <t>269234</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>327735</t>
+          <t>327937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>849316</t>
+          <t>847483</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>937826</t>
+          <t>942486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,97%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180559</t>
+          <t>180883</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>231645</t>
+          <t>235288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>412889</t>
+          <t>416152</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>470694</t>
+          <t>472239</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>611641</t>
+          <t>611367</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>693962</t>
+          <t>692856</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,17%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74003</t>
+          <t>73186</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111042</t>
+          <t>111340</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102811</t>
+          <t>103787</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145688</t>
+          <t>146716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186962</t>
+          <t>185061</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>243984</t>
+          <t>242561</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>430989</t>
+          <t>430401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>488328</t>
+          <t>489454</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>183323</t>
+          <t>180997</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>234829</t>
+          <t>236994</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>631193</t>
+          <t>627468</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>712161</t>
+          <t>711595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>242663</t>
+          <t>243448</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>300071</t>
+          <t>299370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>528919</t>
+          <t>527911</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>595019</t>
+          <t>590613</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>785468</t>
+          <t>784500</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>874535</t>
+          <t>871886</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,62%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96899</t>
+          <t>97322</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139579</t>
+          <t>137863</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100135</t>
+          <t>100385</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139421</t>
+          <t>141850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>209304</t>
+          <t>210211</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267530</t>
+          <t>264759</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>527940</t>
+          <t>527171</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>590765</t>
+          <t>591061</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>338966</t>
+          <t>340023</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>399001</t>
+          <t>401327</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>885299</t>
+          <t>889804</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>978062</t>
+          <t>976236</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,84%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>891280</t>
+          <t>893521</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1000145</t>
+          <t>998833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1965565</t>
+          <t>1966518</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2087090</t>
+          <t>2088174</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2881319</t>
+          <t>2884297</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3047949</t>
+          <t>3053309</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,72%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>398228</t>
+          <t>399242</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>475914</t>
+          <t>480178</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>435303</t>
+          <t>433110</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>517018</t>
+          <t>519327</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>853749</t>
+          <t>857725</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>973490</t>
+          <t>973628</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1987829</t>
+          <t>1985146</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2106482</t>
+          <t>2105949</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>996922</t>
+          <t>1001655</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1112730</t>
+          <t>1109914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3017216</t>
+          <t>3015447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3185352</t>
+          <t>3184731</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2016</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2016 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51264</t>
+          <t>50715</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81024</t>
+          <t>82009</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>214176</t>
+          <t>214064</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>261920</t>
+          <t>264035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>274334</t>
+          <t>271750</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>337363</t>
+          <t>337371</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>157194</t>
+          <t>158401</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>202470</t>
+          <t>205040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225728</t>
+          <t>224006</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>275182</t>
+          <t>272746</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>392548</t>
+          <t>395798</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>464654</t>
+          <t>468263</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>404097</t>
+          <t>401635</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>453895</t>
+          <t>454937</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>165681</t>
+          <t>164507</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>210878</t>
+          <t>209247</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>575412</t>
+          <t>572103</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>647068</t>
+          <t>650099</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,24%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113577</t>
+          <t>112636</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>159618</t>
+          <t>158133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>270703</t>
+          <t>271143</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332714</t>
+          <t>331528</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>399442</t>
+          <t>399163</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>476480</t>
+          <t>473100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>283467</t>
+          <t>282405</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>343739</t>
+          <t>343572</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>386125</t>
+          <t>381411</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>445962</t>
+          <t>446842</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>686048</t>
+          <t>684635</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>770875</t>
+          <t>771850</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>543511</t>
+          <t>541791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>608273</t>
+          <t>606953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>293119</t>
+          <t>296094</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>356599</t>
+          <t>359305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>852667</t>
+          <t>850427</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>951360</t>
+          <t>944217</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>105113</t>
+          <t>104148</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>148054</t>
+          <t>145184</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>254564</t>
+          <t>251278</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>311866</t>
+          <t>306857</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>372719</t>
+          <t>369311</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>441951</t>
+          <t>443945</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182149</t>
+          <t>183541</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>230958</t>
+          <t>231682</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>243330</t>
+          <t>239255</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>297538</t>
+          <t>295791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>440097</t>
+          <t>440556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>512115</t>
+          <t>513473</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>399653</t>
+          <t>400741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>456170</t>
+          <t>454053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203033</t>
+          <t>208357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>257830</t>
+          <t>264067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>618381</t>
+          <t>620733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>697984</t>
+          <t>703060</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86224</t>
+          <t>89063</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>126461</t>
+          <t>128942</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>270995</t>
+          <t>269842</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>332552</t>
+          <t>329493</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>372256</t>
+          <t>373213</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>444855</t>
+          <t>446350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>228098</t>
+          <t>226252</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>280856</t>
+          <t>279098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>298013</t>
+          <t>302831</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>360556</t>
+          <t>359637</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>542973</t>
+          <t>542904</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>625616</t>
+          <t>623139</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>545859</t>
+          <t>543976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>605704</t>
+          <t>604143</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>376294</t>
+          <t>377911</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>440306</t>
+          <t>440519</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>940049</t>
+          <t>943635</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1028376</t>
+          <t>1030316</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>390976</t>
+          <t>388623</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>470578</t>
+          <t>472713</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1059732</t>
+          <t>1070871</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1180103</t>
+          <t>1181127</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1475752</t>
+          <t>1484026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1616346</t>
+          <t>1623633</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>903587</t>
+          <t>901417</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1007929</t>
+          <t>1006557</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1202870</t>
+          <t>1207095</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1314510</t>
+          <t>1330245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2130797</t>
+          <t>2134026</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2288064</t>
+          <t>2299979</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1953610</t>
+          <t>1946076</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2064740</t>
+          <t>2064067</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1091427</t>
+          <t>1100340</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1209526</t>
+          <t>1213283</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3085536</t>
+          <t>3070648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3250429</t>
+          <t>3246187</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,84%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2023</t>
+          <t>Población según si consumen algún tipo de bebida alcohólica al menos una vez al mes en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83177</t>
+          <t>82797</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123234</t>
+          <t>122397</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>226216</t>
+          <t>225082</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>265330</t>
+          <t>265099</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>319021</t>
+          <t>316538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>375065</t>
+          <t>376710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,78%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141837</t>
+          <t>143207</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>187796</t>
+          <t>192858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>205143</t>
+          <t>206199</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245683</t>
+          <t>245137</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>365471</t>
+          <t>362967</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>422778</t>
+          <t>425238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>338760</t>
+          <t>338133</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>394954</t>
+          <t>394473</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>185461</t>
+          <t>183585</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>224826</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>536206</t>
+          <t>536027</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>606133</t>
+          <t>606232</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,32%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66778</t>
+          <t>60718</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>170870</t>
+          <t>172256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>242813</t>
+          <t>245943</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289279</t>
+          <t>290849</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>260546</t>
+          <t>259122</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>460642</t>
+          <t>461166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122509</t>
+          <t>112249</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>319276</t>
+          <t>317130</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>346089</t>
+          <t>344883</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>396271</t>
+          <t>395680</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>411877</t>
+          <t>390524</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>710029</t>
+          <t>707823</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>707562</t>
+          <t>709031</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>996669</t>
+          <t>1016799</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>294840</t>
+          <t>294354</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>344555</t>
+          <t>347812</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>989667</t>
+          <t>990942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1457446</t>
+          <t>1498380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>69,74%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>88391</t>
+          <t>87804</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>131582</t>
+          <t>129928</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>109938</t>
+          <t>127866</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>330677</t>
+          <t>335407</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>225965</t>
+          <t>239295</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>436846</t>
+          <t>433498</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171073</t>
+          <t>173091</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>227631</t>
+          <t>231375</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>117016</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>296803</t>
+          <t>300171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>249714</t>
+          <t>262325</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>497453</t>
+          <t>493312</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,2%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>364609</t>
+          <t>364812</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>428760</t>
+          <t>425164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320393</t>
+          <t>317966</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>720373</t>
+          <t>681076</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>728478</t>
+          <t>731226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1176003</t>
+          <t>1134793</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140637</t>
+          <t>141999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193724</t>
+          <t>197142</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>253829</t>
+          <t>255626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>348346</t>
+          <t>349339</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>428744</t>
+          <t>426223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>524489</t>
+          <t>521349</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191228</t>
+          <t>192495</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>252303</t>
+          <t>252233</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>241739</t>
+          <t>240589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>333735</t>
+          <t>335839</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>468364</t>
+          <t>457949</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>568779</t>
+          <t>565942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>506672</t>
+          <t>501536</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>575021</t>
+          <t>572860</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>422230</t>
+          <t>421128</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>609464</t>
+          <t>591284</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>955576</t>
+          <t>957488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1119440</t>
+          <t>1119780</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,55%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>396396</t>
+          <t>383287</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>565439</t>
+          <t>558848</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>878297</t>
+          <t>890681</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1159343</t>
+          <t>1170070</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1385623</t>
+          <t>1351442</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1711187</t>
+          <t>1693041</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,82%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>635049</t>
+          <t>619525</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>914387</t>
+          <t>910305</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>923005</t>
+          <t>901031</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1216084</t>
+          <t>1212287</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1707113</t>
+          <t>1646294</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2091596</t>
+          <t>2089340</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1996465</t>
+          <t>2003440</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2414665</t>
+          <t>2454165</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1295822</t>
+          <t>1293512</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1857073</t>
+          <t>1861306</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3344938</t>
+          <t>3354584</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4003178</t>
+          <t>4110669</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P29-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P29-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>127758</t>
+          <t>126533</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>170144</t>
+          <t>166979</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>321529</t>
+          <t>321083</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>375105</t>
+          <t>373927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>466552</t>
+          <t>462329</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>531913</t>
+          <t>534958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90213</t>
+          <t>89971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127706</t>
+          <t>127623</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138294</t>
+          <t>136323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>181840</t>
+          <t>181380</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>239540</t>
+          <t>238524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>297360</t>
+          <t>297378</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>413805</t>
+          <t>416321</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>465746</t>
+          <t>464438</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>157740</t>
+          <t>160081</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>202911</t>
+          <t>203939</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>584250</t>
+          <t>580587</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>654985</t>
+          <t>654780</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>198981</t>
+          <t>197761</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>253099</t>
+          <t>254865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>481188</t>
+          <t>480860</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>543259</t>
+          <t>542039</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691133</t>
+          <t>690870</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>779423</t>
+          <t>780788</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134277</t>
+          <t>132967</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>179614</t>
+          <t>176896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>154201</t>
+          <t>154360</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>200587</t>
+          <t>202538</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>300881</t>
+          <t>297720</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>368806</t>
+          <t>364263</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>549197</t>
+          <t>551705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>611277</t>
+          <t>614493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>251159</t>
+          <t>251373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>312930</t>
+          <t>306311</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>812454</t>
+          <t>816129</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>901910</t>
+          <t>903832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,83%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>189354</t>
+          <t>189823</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>242659</t>
+          <t>239307</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>354104</t>
+          <t>354173</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>406059</t>
+          <t>403424</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>561465</t>
+          <t>561125</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>637741</t>
+          <t>636452</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,72%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112907</t>
+          <t>112240</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>153996</t>
+          <t>155388</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151448</t>
+          <t>154503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194717</t>
+          <t>196778</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>278172</t>
+          <t>276885</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>339414</t>
+          <t>338920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>301392</t>
+          <t>305105</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356260</t>
+          <t>358133</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>109860</t>
+          <t>109880</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>152400</t>
+          <t>150267</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>424656</t>
+          <t>428096</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>496661</t>
+          <t>496252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>238561</t>
+          <t>240613</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>294141</t>
+          <t>293090</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>513083</t>
+          <t>516183</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>577850</t>
+          <t>581676</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>766347</t>
+          <t>764220</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>855910</t>
+          <t>853831</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127460</t>
+          <t>126745</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171302</t>
+          <t>170717</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163059</t>
+          <t>165456</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>211396</t>
+          <t>209717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>304605</t>
+          <t>303631</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>368025</t>
+          <t>367948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>499278</t>
+          <t>499199</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560766</t>
+          <t>559686</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>279616</t>
+          <t>276955</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>338183</t>
+          <t>335871</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>786521</t>
+          <t>790352</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>878073</t>
+          <t>878447</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>802564</t>
+          <t>796874</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>900023</t>
+          <t>900685</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1719761</t>
+          <t>1732032</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1847016</t>
+          <t>1841319</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2563608</t>
+          <t>2553101</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2717815</t>
+          <t>2721330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,89%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>503282</t>
+          <t>497623</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>587875</t>
+          <t>581705</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>649158</t>
+          <t>652015</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>746706</t>
+          <t>744606</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1177769</t>
+          <t>1175969</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1307266</t>
+          <t>1307369</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1829096</t>
+          <t>1828370</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1937077</t>
+          <t>1940337</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>842806</t>
+          <t>843828</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>949667</t>
+          <t>948671</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2701121</t>
+          <t>2701679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2862436</t>
+          <t>2867395</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>157287</t>
+          <t>154119</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>206124</t>
+          <t>204845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>393336</t>
+          <t>392413</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>446324</t>
+          <t>448214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>561533</t>
+          <t>561711</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>639351</t>
+          <t>638112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,56%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77646</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114019</t>
+          <t>113990</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83125</t>
+          <t>83430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>121611</t>
+          <t>124482</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173566</t>
+          <t>172166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224707</t>
+          <t>225501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>402516</t>
+          <t>401292</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>456654</t>
+          <t>457273</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>152766</t>
+          <t>152077</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>200626</t>
+          <t>199541</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>565668</t>
+          <t>567950</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>642399</t>
+          <t>642517</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>255846</t>
+          <t>257897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>313260</t>
+          <t>315608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>570513</t>
+          <t>569551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>635198</t>
+          <t>634673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>843274</t>
+          <t>842600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>934712</t>
+          <t>935123</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>115334</t>
+          <t>115386</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>159986</t>
+          <t>160297</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>110225</t>
+          <t>110666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>155148</t>
+          <t>155908</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>236129</t>
+          <t>239635</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>302655</t>
+          <t>304121</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>563704</t>
+          <t>563818</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>630019</t>
+          <t>627427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>269234</t>
+          <t>265686</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>327937</t>
+          <t>328032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>847483</t>
+          <t>845464</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>942486</t>
+          <t>936303</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180883</t>
+          <t>184386</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>235288</t>
+          <t>233719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>416152</t>
+          <t>414849</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>472239</t>
+          <t>472329</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>611367</t>
+          <t>611589</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>692856</t>
+          <t>691206</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73186</t>
+          <t>72132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111340</t>
+          <t>109227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103787</t>
+          <t>102769</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146716</t>
+          <t>146464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>185061</t>
+          <t>189176</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242561</t>
+          <t>244759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>430401</t>
+          <t>430414</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>489454</t>
+          <t>486842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>180997</t>
+          <t>180837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>236994</t>
+          <t>236277</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>627468</t>
+          <t>630143</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>711595</t>
+          <t>707156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,1%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>243448</t>
+          <t>241396</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>299370</t>
+          <t>299080</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>527911</t>
+          <t>526595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>590613</t>
+          <t>593293</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>784500</t>
+          <t>784145</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>871886</t>
+          <t>871934</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,63%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97322</t>
+          <t>98856</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>137863</t>
+          <t>138856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100385</t>
+          <t>100342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141850</t>
+          <t>142274</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210211</t>
+          <t>209545</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>264759</t>
+          <t>269060</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>527171</t>
+          <t>531026</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>591061</t>
+          <t>590885</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>340023</t>
+          <t>341573</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>401327</t>
+          <t>403852</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>889804</t>
+          <t>889496</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>976236</t>
+          <t>981312</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>893521</t>
+          <t>892673</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>998833</t>
+          <t>998843</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1966518</t>
+          <t>1963381</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2088174</t>
+          <t>2080431</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2884297</t>
+          <t>2891285</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3053309</t>
+          <t>3068938</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,95%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>399242</t>
+          <t>398961</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>480178</t>
+          <t>477955</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>433110</t>
+          <t>434993</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>519327</t>
+          <t>516339</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>857725</t>
+          <t>856922</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>973628</t>
+          <t>972565</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1985146</t>
+          <t>1981186</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2105949</t>
+          <t>2098895</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1001655</t>
+          <t>996368</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1109914</t>
+          <t>1109880</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3015447</t>
+          <t>3001921</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3184731</t>
+          <t>3184643</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,6%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50715</t>
+          <t>52023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82009</t>
+          <t>82712</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>214064</t>
+          <t>213864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>264035</t>
+          <t>265501</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>271750</t>
+          <t>275577</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>337371</t>
+          <t>334578</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>158401</t>
+          <t>158439</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>205040</t>
+          <t>205094</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224006</t>
+          <t>226964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>272746</t>
+          <t>276353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>395798</t>
+          <t>392833</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>468263</t>
+          <t>462190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>401635</t>
+          <t>402836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>454937</t>
+          <t>454652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164507</t>
+          <t>162914</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>209247</t>
+          <t>210359</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>572103</t>
+          <t>579372</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>650099</t>
+          <t>653315</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,48%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>112636</t>
+          <t>109526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>158133</t>
+          <t>157521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>271143</t>
+          <t>275245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>331528</t>
+          <t>334988</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>399163</t>
+          <t>402625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>473100</t>
+          <t>477822</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>282405</t>
+          <t>283859</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>343572</t>
+          <t>346290</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381411</t>
+          <t>382529</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>446842</t>
+          <t>446670</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>684635</t>
+          <t>680433</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>771850</t>
+          <t>772553</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,44%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>541791</t>
+          <t>541388</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>606953</t>
+          <t>606585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>296094</t>
+          <t>294512</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>359305</t>
+          <t>356764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>850427</t>
+          <t>854513</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>944217</t>
+          <t>943548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104148</t>
+          <t>106047</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145184</t>
+          <t>148991</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>251278</t>
+          <t>253193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>306857</t>
+          <t>308826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>369311</t>
+          <t>372074</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>443945</t>
+          <t>443497</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>183541</t>
+          <t>182619</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231682</t>
+          <t>233177</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>239255</t>
+          <t>240141</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>295791</t>
+          <t>293935</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>440556</t>
+          <t>439991</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>513473</t>
+          <t>515244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>400741</t>
+          <t>398911</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>454053</t>
+          <t>456749</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>208357</t>
+          <t>207087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>264067</t>
+          <t>260864</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>620733</t>
+          <t>624360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>703060</t>
+          <t>704824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>89063</t>
+          <t>87550</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128942</t>
+          <t>127264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>269842</t>
+          <t>273780</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>329493</t>
+          <t>334071</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>373213</t>
+          <t>369393</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>446350</t>
+          <t>444944</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>226252</t>
+          <t>226783</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>279098</t>
+          <t>280378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>302831</t>
+          <t>301478</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>359637</t>
+          <t>362057</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>542904</t>
+          <t>545326</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>623139</t>
+          <t>629639</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>543976</t>
+          <t>545810</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>604143</t>
+          <t>604071</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>377911</t>
+          <t>379709</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>440519</t>
+          <t>443393</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>943635</t>
+          <t>939117</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1030316</t>
+          <t>1028056</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,03%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>388623</t>
+          <t>390363</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>472713</t>
+          <t>473128</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1070871</t>
+          <t>1061831</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1181127</t>
+          <t>1178938</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1484026</t>
+          <t>1486244</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1623633</t>
+          <t>1624104</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>901417</t>
+          <t>900709</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1006557</t>
+          <t>1009819</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1207095</t>
+          <t>1206070</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1330245</t>
+          <t>1323384</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2134026</t>
+          <t>2135072</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2299979</t>
+          <t>2291141</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1946076</t>
+          <t>1946450</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2064067</t>
+          <t>2064329</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1100340</t>
+          <t>1094164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1213283</t>
+          <t>1212388</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3070648</t>
+          <t>3074050</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3246187</t>
+          <t>3240334</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,76%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>100353</t>
+          <t>121586</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82797</t>
+          <t>102063</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122397</t>
+          <t>146557</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>245154</t>
+          <t>268584</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>225082</t>
+          <t>248159</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>265099</t>
+          <t>288813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>345507</t>
+          <t>390171</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>316538</t>
+          <t>357531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>376710</t>
+          <t>423074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>164897</t>
+          <t>176198</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143207</t>
+          <t>152630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>192858</t>
+          <t>200782</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>226108</t>
+          <t>242294</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>206199</t>
+          <t>221738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>245137</t>
+          <t>265085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>391006</t>
+          <t>418492</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>362967</t>
+          <t>385148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>425238</t>
+          <t>449743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>368395</t>
+          <t>391090</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>338133</t>
+          <t>361031</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>394473</t>
+          <t>419291</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>203894</t>
+          <t>221556</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>183585</t>
+          <t>201103</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>223438</t>
+          <t>241826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>572288</t>
+          <t>612646</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>536027</t>
+          <t>579501</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>606232</t>
+          <t>651452</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>633645</t>
+          <t>688874</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>633645</t>
+          <t>688874</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>633645</t>
+          <t>688874</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>675156</t>
+          <t>732434</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>675156</t>
+          <t>732434</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>675156</t>
+          <t>732434</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1308801</t>
+          <t>1421309</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1308801</t>
+          <t>1421309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1308801</t>
+          <t>1421309</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>128740</t>
+          <t>166558</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60718</t>
+          <t>141363</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172256</t>
+          <t>195114</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>268163</t>
+          <t>305975</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>245943</t>
+          <t>278996</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>290849</t>
+          <t>331177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>396902</t>
+          <t>472533</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>259122</t>
+          <t>435512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>461166</t>
+          <t>507735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>245695</t>
+          <t>269462</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>112249</t>
+          <t>240500</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>317130</t>
+          <t>305255</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>369086</t>
+          <t>410618</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>344883</t>
+          <t>383196</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>395680</t>
+          <t>438009</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>614781</t>
+          <t>680080</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>390524</t>
+          <t>637763</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>707823</t>
+          <t>722331</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>817315</t>
+          <t>611714</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>709031</t>
+          <t>575999</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1016799</t>
+          <t>647112</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>319405</t>
+          <t>352619</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>294354</t>
+          <t>327793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>347812</t>
+          <t>381474</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1136720</t>
+          <t>964333</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>990942</t>
+          <t>918274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1498380</t>
+          <t>1010593</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1191750</t>
+          <t>1047733</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1191750</t>
+          <t>1047733</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1191750</t>
+          <t>1047733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>956654</t>
+          <t>1069213</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>956654</t>
+          <t>1069213</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>956654</t>
+          <t>1069213</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2148404</t>
+          <t>2116946</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2148404</t>
+          <t>2116946</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2148404</t>
+          <t>2116946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>107264</t>
+          <t>146299</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87804</t>
+          <t>121786</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>129928</t>
+          <t>170196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>242438</t>
+          <t>259157</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>127866</t>
+          <t>234609</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>335407</t>
+          <t>284989</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>349702</t>
+          <t>405456</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>239295</t>
+          <t>370997</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>433498</t>
+          <t>440532</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>198219</t>
+          <t>213772</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>173091</t>
+          <t>186746</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231375</t>
+          <t>244302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>224535</t>
+          <t>256924</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117016</t>
+          <t>232104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>300171</t>
+          <t>279644</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>422754</t>
+          <t>470695</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>262325</t>
+          <t>433108</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>493312</t>
+          <t>509145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>396836</t>
+          <t>439567</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>364812</t>
+          <t>405797</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>425164</t>
+          <t>470127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>464113</t>
+          <t>293557</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>317966</t>
+          <t>269431</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681076</t>
+          <t>320794</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>860949</t>
+          <t>733124</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>731226</t>
+          <t>690551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1134793</t>
+          <t>773680</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>48,08%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>702319</t>
+          <t>799637</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>702319</t>
+          <t>799637</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>702319</t>
+          <t>799637</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>931086</t>
+          <t>809638</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>931086</t>
+          <t>809638</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>931086</t>
+          <t>809638</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1633405</t>
+          <t>1609275</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1633405</t>
+          <t>1609275</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1633405</t>
+          <t>1609275</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>165550</t>
+          <t>186293</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141999</t>
+          <t>163435</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>197142</t>
+          <t>219325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>313672</t>
+          <t>352747</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>255626</t>
+          <t>324633</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>349339</t>
+          <t>381849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>479222</t>
+          <t>539040</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>426223</t>
+          <t>497533</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>521349</t>
+          <t>579757</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>219118</t>
+          <t>235180</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192495</t>
+          <t>207174</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>252233</t>
+          <t>266275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>302690</t>
+          <t>324352</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>240589</t>
+          <t>296296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>335839</t>
+          <t>352007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>521808</t>
+          <t>559531</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>457949</t>
+          <t>519982</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>565942</t>
+          <t>600074</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>541077</t>
+          <t>567493</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>501536</t>
+          <t>530898</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>572860</t>
+          <t>601178</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>473711</t>
+          <t>438495</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>421128</t>
+          <t>408231</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>591284</t>
+          <t>469395</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1014787</t>
+          <t>1005987</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>957488</t>
+          <t>959435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1119780</t>
+          <t>1052300</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>50,0%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>925745</t>
+          <t>988965</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>925745</t>
+          <t>988965</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>925745</t>
+          <t>988965</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1090072</t>
+          <t>1115594</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1090072</t>
+          <t>1115594</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1090072</t>
+          <t>1115594</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2015817</t>
+          <t>2104559</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2015817</t>
+          <t>2104559</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2015817</t>
+          <t>2104559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>501907</t>
+          <t>620735</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>383287</t>
+          <t>573167</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>558848</t>
+          <t>673246</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1069426</t>
+          <t>1186464</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>890681</t>
+          <t>1135671</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1170070</t>
+          <t>1236540</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1571333</t>
+          <t>1807199</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1351442</t>
+          <t>1730388</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1693041</t>
+          <t>1888447</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>827929</t>
+          <t>894611</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>619525</t>
+          <t>839228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>910305</t>
+          <t>950519</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1122419</t>
+          <t>1234188</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>901031</t>
+          <t>1188050</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1212287</t>
+          <t>1285005</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1950349</t>
+          <t>2128799</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1646294</t>
+          <t>2053410</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2089340</t>
+          <t>2203237</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2123623</t>
+          <t>2009863</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2003440</t>
+          <t>1945994</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2454165</t>
+          <t>2077599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1461122</t>
+          <t>1306227</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1293512</t>
+          <t>1254090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1861306</t>
+          <t>1359916</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3584745</t>
+          <t>3316090</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3354584</t>
+          <t>3233662</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4110669</t>
+          <t>3410022</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>47,02%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3453459</t>
+          <t>3525209</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3453459</t>
+          <t>3525209</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3453459</t>
+          <t>3525209</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3652968</t>
+          <t>3726879</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3652968</t>
+          <t>3726879</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3652968</t>
+          <t>3726879</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7106427</t>
+          <t>7252088</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7106427</t>
+          <t>7252088</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7106427</t>
+          <t>7252088</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
